--- a/Assets/결과/#2 장애물 작은 거/TestControllerAgent_Origin(Clone)1_vs_TestTotalAgent_MissReward(Clone)2.xlsx
+++ b/Assets/결과/#2 장애물 작은 거/TestControllerAgent_Origin(Clone)1_vs_TestTotalAgent_MissReward(Clone)2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dltrn\Github\Unity-MLAgents-FPS\Assets\결과\#2 장애물 작은 거\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480142BC-4029-4532-8888-04F782CDE5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6919402-6593-474B-BBC1-AB61BD8C411B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="3072" windowWidth="15792" windowHeight="9960" xr2:uid="{E2ADF703-4882-4A3F-BAAC-D69B828E7967}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E2ADF703-4882-4A3F-BAAC-D69B828E7967}"/>
   </bookViews>
   <sheets>
     <sheet name="TestControllerAgent_Origin(Clon" sheetId="1" r:id="rId1"/>
